--- a/data/wfa_summary_2024-10-21_2026-04-20.xlsx
+++ b/data/wfa_summary_2024-10-21_2026-04-20.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="8e5e07ae-10a2-42cb-b008-404f03f" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="b1144083-e8a4-4061-892a-3774e81" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -49,7 +49,7 @@
     <t xml:space="preserve">best_indicators_by_sector</t>
   </si>
   <si>
-    <t xml:space="preserve">Energi: MA Crossover; Finansial: MA Crossover; Industri: MA Crossover; Teknologi: MA Crossover</t>
+    <t xml:space="preserve">Energi: MA Crossover; Finansial: RSI; Industri: MA Crossover; Teknologi: MA Crossover</t>
   </si>
 </sst>
 </file>
@@ -262,7 +262,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="19.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="81.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="73.23"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -299,25 +299,25 @@
         <v>4</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>58.1891025641026</v>
+        <v>57.521645021645</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>58.5798816568047</v>
+        <v>57.2815533980583</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>51.9230769230769</v>
+        <v>50</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>71.4285714285714</v>
       </c>
       <c r="I2" s="0" t="s">
         <v>9</v>
